--- a/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
@@ -1,17 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Betygsskalor'!$A$1:$E$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,126 +462,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25F</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor: kursnivå U,3,4,5 men delmoment i U,G,VG</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25F</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2J4</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor: kursnivå U,3,4,5 men delmoment i U,G,VG</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2J4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2L8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor: kursnivå U,3,4,5 men delmoment i U,G,VG</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2L8</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GSQ2PH</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Inkonsekvent delskalor: kursnivå U,3,4,5 men delmoment i U,G,VG</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2PH</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Betygsskalor" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Betygsskalor.xlsx
@@ -425,14 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,15 +450,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
